--- a/output/pdf_financials_xlsx/BLU.xlsx
+++ b/output/pdf_financials_xlsx/BLU.xlsx
@@ -1660,7 +1660,7 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.666456</v>
       </c>
     </row>
     <row r="93">
@@ -2600,7 +2600,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BLU.xlsx
+++ b/output/pdf_financials_xlsx/BLU.xlsx
@@ -582,7 +582,7 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.027525</v>
       </c>
     </row>
     <row r="13">
@@ -785,7 +785,7 @@
         <v>-0.658538</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.662646</v>
+        <v>-0.690171</v>
       </c>
     </row>
     <row r="28">
@@ -811,7 +811,7 @@
         <v>-0.658538</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.662646</v>
+        <v>-0.690171</v>
       </c>
     </row>
     <row r="30">
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.144521</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.497487</v>
       </c>
     </row>
     <row r="35">
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.144521</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.497487</v>
       </c>
     </row>
     <row r="37">
@@ -1057,10 +1057,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1.233016</v>
+        <v>0.088495</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.659721</v>
+        <v>0.162234</v>
       </c>
     </row>
     <row r="49">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3742,7 +3742,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
